--- a/Avaliações dos Itens/Avaliações (2008-2024)/2013.xlsx
+++ b/Avaliações dos Itens/Avaliações (2008-2024)/2013.xlsx
@@ -2,18 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a040bb1f01841a5/Desktop/Educomp 2026/Análises/Avaliação 1/criterios por questoes e provas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{A0F51385-EAD1-4930-9556-2866AB8B9317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B291A36-8B0B-4985-997E-EB4C4EE45340}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A0F51385-EAD1-4930-9556-2866AB8B9317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9F6E0F5-60A6-420E-AC9C-77387E186322}"/>
   <bookViews>
     <workbookView xWindow="29388" yWindow="-81" windowWidth="29698" windowHeight="16094" xr2:uid="{F707F352-404B-409B-94EA-AE37440C9E6C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="2013" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -708,5 +703,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>